--- a/agenda_territorial_consolidada.xlsx
+++ b/agenda_territorial_consolidada.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1973,7 +1973,11 @@
           <t>Alto Valle</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Sin especificar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jornada de integración y paneles provinciales compuestas por visitas a sitios estratégicos para el desarrollo de la provincia, encuentros con funcionarias/os y referentes locales y actividades de integración grupal con los participantes de la formación Gestión para el Desarrollo.</t>
@@ -2032,7 +2036,11 @@
           <t>Alto Valle</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sin especificar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Jornada de integración y paneles provinciales compuestas por visitas a sitios estratégicos para el desarrollo de la provincia, encuentros con funcionarias/os y referentes locales y actividades de integración grupal con los participantes de la formación Gestión para el Desarrollo.</t>
@@ -2131,7 +2139,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>ALTA</t>
@@ -2164,6 +2176,61 @@
         <v>100</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>34</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Firma de Convienio con IAPG</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>IAPG | SEEyA | Ministerio de Educación y DDHH</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>General Roca</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>CET 1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="n">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/agenda_territorial_consolidada.xlsx
+++ b/agenda_territorial_consolidada.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2231,6 +2231,61 @@
         <v>50</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>35</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>YPF por ONU HABITAT</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>YPF | ONU-Hábitat | Secretaría de Ambiente | UNRN-Arquitectura</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Sin especificar</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>General Roca</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>UNRN</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/agenda_territorial_consolidada.xlsx
+++ b/agenda_territorial_consolidada.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2286,6 +2286,57 @@
         <v>50</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>37</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Maquetas V4LE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Sin especificar</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Cipolletti</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Capacitación para el armado y el uso de las Maquetas V4LE.</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/agenda_territorial_consolidada.xlsx
+++ b/agenda_territorial_consolidada.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2337,6 +2337,57 @@
         <v>50</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>37</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Maquetas V4LE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Sin especificar</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>General Roca</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Capacitación para docentes para el armado y uso de las Maquetas V4LE.</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/agenda_territorial_consolidada.xlsx
+++ b/agenda_territorial_consolidada.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -965,7 +965,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sin especificar (Agosto 2026)</t>
+          <t>Sin especificar (A coordinar)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -973,22 +973,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Entrega de certificados Programación</t>
+          <t xml:space="preserve">Entrega de certificados Programación </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Río Colorado</t>
+          <t>Cinco Saltos</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SEEyA | UBA | Municipalidad de Río Colorado</t>
+          <t>SEEyA | UBA | Municipalidad de Cinco Saltos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.30-Entrega de certificados con autoridades</t>
+          <t>Entrega de certificados con autoridades</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Gobernador + Secretaria de EEYA + Funcionarios</t>
+          <t>Gobernador + Secretaria de EEYA + fFuncionarios</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Río Colorado</t>
+          <t>Cinco Saltos</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1042,36 +1042,36 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sin especificar (A coordinar)</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entrega de certificados Programación </t>
+          <t>Expo Universitaria</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cinco Saltos</t>
+          <t>Sierra Grande</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SEEyA | UBA | Municipalidad de Cinco Saltos</t>
+          <t>SEEyA | Ministerio de Educación y DDHH | Municipalidad de Sierra Grande | Fundación YPF</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entrega de certificados con autoridades</t>
+          <t>Feria y exposiciones sobre carreras universitarios y formación terciaria</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Jóvenes y adultos</t>
+          <t>Estudiantes de nivel secundario y público en general</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1101,62 +1101,54 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Gobernador + Secretaria de EEYA + fFuncionarios</t>
+          <t>Gobernador + Secretaria de EEyA + Ministra de Educación + Funcionarios</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Cinco Saltos</t>
+          <t>Sierra Grande</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>Gimnasio Vuta Mahuida</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Acto de entrega de certificados de la Diplomatura en Iniciación a la Programación y Análisis de Datos</t>
+          <t>Feria y exposiciones sobre carreras universitarios y formación terciaria</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Expo Universitaria</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Sierra Grande</t>
-        </is>
-      </c>
+          <t>Plenario del CIN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SEEyA | Ministerio de Educación y DDHH | Municipalidad de Sierra Grande | Fundación YPF</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Feria y exposiciones sobre carreras universitarios y formación terciaria</t>
-        </is>
-      </c>
+          <t>UNRN</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -1164,7 +1156,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Estudiantes de nivel secundario y público en general</t>
+          <t>Rectores de universidades de todo el país</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1172,63 +1164,55 @@
           <t>ALTA</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>AGOSTO</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>En curso</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Gobernador + Secretaria de EEyA + Ministra de Educación + Funcionarios</t>
+          <t xml:space="preserve">Gobernador </t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>Sin especificar</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Sierra Grande</t>
+          <t>San Carlos de Bariloche</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Gimnasio Vuta Mahuida</t>
+          <t>Sin especificar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Feria y exposiciones sobre carreras universitarios y formación terciaria</t>
+          <t>El fin será contribuir con la elaboración de agendas institucionales y de política pública para el fortalecimiento de una educación superior democrática, federal y socialmente comprometida.</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>Sin especificar (A coordinar)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plenario del CIN</t>
+          <t>Entrega de certificados Programación</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UNRN</t>
+          <t>SEEyA | UBA | Municipalidad de Sierra Grande</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1239,7 +1223,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Rectores de universidades de todo el país</t>
+          <t>Jóvenes y adultos</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1251,7 +1235,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gobernador </t>
+          <t>Gobernador + Secretaria de EEyA</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1261,21 +1245,21 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>San Carlos de Bariloche</t>
+          <t>Sierra Grande</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>Gimnasio Vuta Mahuida</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>El fin será contribuir con la elaboración de agendas institucionales y de política pública para el fortalecimiento de una educación superior democrática, federal y socialmente comprometida.</t>
+          <t>Acto de entrega de certificados de la Diplomatura en Iniciación a la Programación y Análisis de Datos</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -1295,7 +1279,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SEEyA | UBA | Municipalidad de Sierra Grande</t>
+          <t>SEEyA | UBA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1318,7 +1302,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Gobernador + Secretaria de EEyA</t>
+          <t>Gobernador + Secretaria EEyA + Funcionarios</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1328,12 +1312,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Sierra Grande</t>
+          <t>General Roca</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Gimnasio Vuta Mahuida</t>
+          <t>Sin especificar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1342,27 +1326,27 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sin especificar (A coordinar)</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Entrega de certificados Programación</t>
+          <t>Plenario del CIN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SEEyA | UBA</t>
+          <t>UNRN</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1373,7 +1357,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Jóvenes y adultos</t>
+          <t>Rectores de universidades de todo el país</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1385,7 +1369,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Gobernador + Secretaria EEyA + Funcionarios</t>
+          <t>Gobernador</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1395,114 +1379,110 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>General Roca</t>
+          <t>San Carlos de Bariloche</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>Sin espeficificar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Acto de entrega de certificados de la Diplomatura en Iniciación a la Programación y Análisis de Datos</t>
+          <t>El fin será contribuir con la elaboración de agendas institucionales y de política pública para el fortalecimiento de una educación superior democrática, federal y socialmente comprometida.</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plenario del CIN</t>
+          <t>Diplomatura en Iniciación a la Programación y Análisis de Datos</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UNRN</t>
+          <t>SEEyA | UBA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Rectores de universidades de todo el país</t>
+          <t>Jóvenes y adultos</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>INTERMEDIA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Gobernador</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>San Carlos de Bariloche</t>
+          <t>General Roca</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin espeficificar</t>
+          <t>CET 33</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>El fin será contribuir con la elaboración de agendas institucionales y de política pública para el fortalecimiento de una educación superior democrática, federal y socialmente comprometida.</t>
+          <t>Clase presencial</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Diplomatura en Iniciación a la Programación y Análisis de Datos</t>
+          <t>Diplomatura en Iniciación a la Programación y Analisis de Datos</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SEEyA | UBA</t>
+          <t>SEEyA | UBA | Municipio de Río Colorado</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1520,17 +1500,17 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>General Roca</t>
+          <t>Río Colorado</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>CET 33</t>
+          <t>CERC C/ H. Yrigoyen y Belgrano</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1539,33 +1519,33 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Diplomatura en Iniciación a la Programación y Analisis de Datos</t>
+          <t>Diplomatura en Iniciación a la Programación y Análisis de Datos</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SEEyA | UBA | Municipio de Río Colorado</t>
+          <t>SEEyA | UBA | Municipalidad de Sierra Grande</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1583,17 +1563,17 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Río Colorado</t>
+          <t>Sierra Grande</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>CERC C/ H. Yrigoyen y Belgrano</t>
+          <t>CIC C/ Amancay y Canchas Calvo</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1602,17 +1582,17 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1622,7 +1602,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SEEyA | UBA | Municipalidad de Sierra Grande</t>
+          <t>SEEyA | UBA | Municipalidad de Cinco Saltos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1651,12 +1631,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Sierra Grande</t>
+          <t>Cinco Saltos</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>CIC C/ Amancay y Canchas Calvo</t>
+          <t>Escuela Primaria N° 291 C/ Pedro Ramos 849</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1665,38 +1645,38 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Diplomatura en Iniciación a la Programación y Análisis de Datos</t>
+          <t>Lanzamiento Dot conecta</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SEEyA | UBA | Municipalidad de Cinco Saltos</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Jóvenes y adultos</t>
+          <t>General</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1709,46 +1689,42 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>Sin especificar</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Cinco Saltos</t>
+          <t>General Roca</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Escuela Primaria N° 291 C/ Pedro Ramos 849</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Clase presencial</t>
-        </is>
-      </c>
+          <t>Diario Rio Negro</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lanzamiento Dot conecta</t>
+          <t>Plenario del CIN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Universidad Nacional de Río Negro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1764,12 +1740,16 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>INTERMEDIA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gobernador </t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>Sin especificar</t>
@@ -1777,15 +1757,19 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>General Roca</t>
+          <t>San Carlos de Bariloche</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Diario Rio Negro</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+          <t>Sin especificar</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>El fin será contribuir con la elaboración de agendas institucionales y de política pública para el fortalecimiento de una educación superior democrática, federal y socialmente comprometida.</t>
+        </is>
+      </c>
       <c r="Q19" t="n">
         <v>50</v>
       </c>
@@ -1793,21 +1777,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plenario del CIN</t>
+          <t>Hackaton</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Universidad Nacional de Río Negro</t>
+          <t>SEEyA | Alkemy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1818,7 +1802,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Jóvenes y adultos</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1830,27 +1814,27 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gobernador </t>
+          <t>Gobernador | Secretaria de Energía</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>San Carlos de Bariloche</t>
+          <t>Cipolletti</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>Secretaría de Estado de Energía y Ambiente</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>El fin será contribuir con la elaboración de agendas institucionales y de política pública para el fortalecimiento de una educación superior democrática, federal y socialmente comprometida.</t>
+          <t>La actividad consistirá en una jornada colaborativa en la que los participantes, organizados en equipos, trabajarán sobre desafíos concretos para desarrollar una solución innovadora. A lo largo del encuentro, contarán con una instancia de ideación, desarrollo y preparación de la propuesta. Para finalizar, cada equipo presentará su solución ante un jurado, que seleccionará al equipo ganador.</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -1860,7 +1844,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1868,13 +1852,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hackaton</t>
+          <t>Jornada CFI - Gestión para el Desarrollo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SEEyA | Alkemy</t>
+          <t>CFI | SEEyA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1885,7 +1869,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Jóvenes y adultos</t>
+          <t>Jóvenes</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1895,39 +1879,35 @@
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Gobernador | Secretaria de Energía</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>Sin especificar</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Cipolletti</t>
+          <t>Alto Valle</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Secretaría de Estado de Energía y Ambiente</t>
+          <t>Sin especificar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>La actividad consistirá en una jornada colaborativa en la que los participantes, organizados en equipos, trabajarán sobre desafíos concretos para desarrollar una solución innovadora. A lo largo del encuentro, contarán con una instancia de ideación, desarrollo y preparación de la propuesta. Para finalizar, cada equipo presentará su solución ante un jurado, que seleccionará al equipo ganador.</t>
+          <t>Jornada de integración y paneles provinciales compuestas por visitas a sitios estratégicos para el desarrollo de la provincia, encuentros con funcionarias/os y referentes locales y actividades de integración grupal con los participantes de la formación Gestión para el Desarrollo.</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1941,7 +1921,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CFI | SEEyA</t>
+          <t>CFI | SEEyE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1990,21 +1970,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jornada CFI - Gestión para el Desarrollo</t>
+          <t>I Foro de la Juventud Rionegrina</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CFI | SEEyE</t>
+          <t>Varios</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -2033,27 +2013,27 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Alto Valle</t>
+          <t>Cipolletti</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>Escuela Manuel Belgrano | CCC</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Jornada de integración y paneles provinciales compuestas por visitas a sitios estratégicos para el desarrollo de la provincia, encuentros con funcionarias/os y referentes locales y actividades de integración grupal con los participantes de la formación Gestión para el Desarrollo.</t>
+          <t xml:space="preserve">Primer Foro de la Juventud Rionegrina que reúne a jóvenes de toda la provincia para debatir, proponer y pensar la provincia. </t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2078,7 +2058,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Jóvenes</t>
+          <t>General</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2116,21 +2096,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>I Foro de la Juventud Rionegrina</t>
+          <t>Firma de Convienio con IAPG</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Varios</t>
+          <t>IAPG | SEEyA | Ministerio de Educación y DDHH</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2139,11 +2119,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>ALTA</t>
@@ -2154,46 +2130,42 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Cipolletti</t>
+          <t>General Roca</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Escuela Manuel Belgrano | CCC</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Primer Foro de la Juventud Rionegrina que reúne a jóvenes de toda la provincia para debatir, proponer y pensar la provincia. </t>
-        </is>
-      </c>
+          <t>CET 1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Firma de Convienio con IAPG</t>
+          <t>YPF por ONU HABITAT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAPG | SEEyA | Ministerio de Educación y DDHH</t>
+          <t>YPF | ONU-Hábitat | Secretaría de Ambiente | UNRN-Arquitectura</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2213,7 +2185,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>Sin especificar</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2223,7 +2195,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>CET 1</t>
+          <t>UNRN</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2234,23 +2206,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>YPF por ONU HABITAT</t>
+          <t>Maquetas V4LE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>YPF | ONU-Hábitat | Secretaría de Ambiente | UNRN-Arquitectura</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
@@ -2273,15 +2241,15 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>General Roca</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>UNRN</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
+          <t>Cipolletti</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Capacitación para el armado y el uso de las Maquetas V4LE.</t>
+        </is>
+      </c>
       <c r="Q27" t="n">
         <v>50</v>
       </c>
@@ -2289,7 +2257,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2324,67 +2292,16 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Cipolletti</t>
+          <t>General Roca</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Capacitación para el armado y el uso de las Maquetas V4LE.</t>
+          <t>Capacitación para docentes para el armado y uso de las Maquetas V4LE.</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>37</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Maquetas V4LE</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Sin especificar</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>General Roca</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Capacitación para docentes para el armado y uso de las Maquetas V4LE.</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
         <v>50</v>
       </c>
     </row>

--- a/agenda_territorial_consolidada.xlsx
+++ b/agenda_territorial_consolidada.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -965,30 +965,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sin especificar (A coordinar)</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entrega de certificados Programación </t>
+          <t>Expo Universitaria</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cinco Saltos</t>
+          <t>Sierra Grande</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SEEyA | UBA | Municipalidad de Cinco Saltos</t>
+          <t>SEEyA | Ministerio de Educación y DDHH | Municipalidad de Sierra Grande | Fundación YPF</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entrega de certificados con autoridades</t>
+          <t>Feria y exposiciones sobre carreras universitarios y formación terciaria</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jóvenes y adultos</t>
+          <t>Estudiantes de nivel secundario y público en general</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1018,62 +1018,54 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Gobernador + Secretaria de EEYA + fFuncionarios</t>
+          <t>Gobernador + Secretaria de EEyA + Ministra de Educación + Funcionarios</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Cinco Saltos</t>
+          <t>Sierra Grande</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>Gimnasio Vuta Mahuida</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Acto de entrega de certificados de la Diplomatura en Iniciación a la Programación y Análisis de Datos</t>
+          <t>Feria y exposiciones sobre carreras universitarios y formación terciaria</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Expo Universitaria</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Sierra Grande</t>
-        </is>
-      </c>
+          <t>Plenario del CIN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SEEyA | Ministerio de Educación y DDHH | Municipalidad de Sierra Grande | Fundación YPF</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Feria y exposiciones sobre carreras universitarios y formación terciaria</t>
-        </is>
-      </c>
+          <t>UNRN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -1081,7 +1073,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Estudiantes de nivel secundario y público en general</t>
+          <t>Rectores de universidades de todo el país</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1089,63 +1081,55 @@
           <t>ALTA</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>AGOSTO</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>En curso</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Gobernador + Secretaria de EEyA + Ministra de Educación + Funcionarios</t>
+          <t xml:space="preserve">Gobernador </t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>Sin especificar</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Sierra Grande</t>
+          <t>San Carlos de Bariloche</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Gimnasio Vuta Mahuida</t>
+          <t>Sin especificar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Feria y exposiciones sobre carreras universitarios y formación terciaria</t>
+          <t>El fin será contribuir con la elaboración de agendas institucionales y de política pública para el fortalecimiento de una educación superior democrática, federal y socialmente comprometida.</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>Sin especificar (A coordinar)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plenario del CIN</t>
+          <t>Entrega de certificados Programación</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UNRN</t>
+          <t>SEEyA | UBA | Municipalidad de Sierra Grande</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1156,7 +1140,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Rectores de universidades de todo el país</t>
+          <t>Jóvenes y adultos</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1168,7 +1152,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gobernador </t>
+          <t>Gobernador + Secretaria de EEyA</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1178,21 +1162,21 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>San Carlos de Bariloche</t>
+          <t>Sierra Grande</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>Gimnasio Vuta Mahuida</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>El fin será contribuir con la elaboración de agendas institucionales y de política pública para el fortalecimiento de una educación superior democrática, federal y socialmente comprometida.</t>
+          <t>Acto de entrega de certificados de la Diplomatura en Iniciación a la Programación y Análisis de Datos</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -1212,7 +1196,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SEEyA | UBA | Municipalidad de Sierra Grande</t>
+          <t>SEEyA | UBA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1235,7 +1219,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Gobernador + Secretaria de EEyA</t>
+          <t>Gobernador + Secretaria EEyA + Funcionarios</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1245,12 +1229,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Sierra Grande</t>
+          <t>General Roca</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Gimnasio Vuta Mahuida</t>
+          <t>Sin especificar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1259,27 +1243,27 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sin especificar (A coordinar)</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Entrega de certificados Programación</t>
+          <t>Plenario del CIN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SEEyA | UBA</t>
+          <t>UNRN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1290,7 +1274,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Jóvenes y adultos</t>
+          <t>Rectores de universidades de todo el país</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1302,7 +1286,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Gobernador + Secretaria EEyA + Funcionarios</t>
+          <t>Gobernador</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1312,114 +1296,110 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>General Roca</t>
+          <t>San Carlos de Bariloche</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>Sin espeficificar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Acto de entrega de certificados de la Diplomatura en Iniciación a la Programación y Análisis de Datos</t>
+          <t>El fin será contribuir con la elaboración de agendas institucionales y de política pública para el fortalecimiento de una educación superior democrática, federal y socialmente comprometida.</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plenario del CIN</t>
+          <t>Diplomatura en Iniciación a la Programación y Análisis de Datos</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UNRN</t>
+          <t>SEEyA | UBA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Rectores de universidades de todo el país</t>
+          <t>Jóvenes y adultos</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>INTERMEDIA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Gobernador</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>San Carlos de Bariloche</t>
+          <t>General Roca</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin espeficificar</t>
+          <t>CET 33</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>El fin será contribuir con la elaboración de agendas institucionales y de política pública para el fortalecimiento de una educación superior democrática, federal y socialmente comprometida.</t>
+          <t>Clase presencial</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Diplomatura en Iniciación a la Programación y Análisis de Datos</t>
+          <t>Diplomatura en Iniciación a la Programación y Analisis de Datos</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SEEyA | UBA</t>
+          <t>SEEyA | UBA | Municipio de Río Colorado</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1437,17 +1417,17 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>General Roca</t>
+          <t>Río Colorado</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>CET 33</t>
+          <t>CERC C/ H. Yrigoyen y Belgrano</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1456,33 +1436,33 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Diplomatura en Iniciación a la Programación y Analisis de Datos</t>
+          <t>Diplomatura en Iniciación a la Programación y Análisis de Datos</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SEEyA | UBA | Municipio de Río Colorado</t>
+          <t>SEEyA | UBA | Municipalidad de Sierra Grande</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1500,17 +1480,17 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Río Colorado</t>
+          <t>Sierra Grande</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>CERC C/ H. Yrigoyen y Belgrano</t>
+          <t>CIC C/ Amancay y Canchas Calvo</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1519,17 +1499,17 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1539,7 +1519,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SEEyA | UBA | Municipalidad de Sierra Grande</t>
+          <t>SEEyA | UBA | Municipalidad de Cinco Saltos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1568,12 +1548,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Sierra Grande</t>
+          <t>Cinco Saltos</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>CIC C/ Amancay y Canchas Calvo</t>
+          <t>Escuela Primaria N° 291 C/ Pedro Ramos 849</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1582,38 +1562,38 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Diplomatura en Iniciación a la Programación y Análisis de Datos</t>
+          <t>Lanzamiento Dot conecta</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SEEyA | UBA | Municipalidad de Cinco Saltos</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Jóvenes y adultos</t>
+          <t>General</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1626,46 +1606,42 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>Sin especificar</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Cinco Saltos</t>
+          <t>General Roca</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Escuela Primaria N° 291 C/ Pedro Ramos 849</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Clase presencial</t>
-        </is>
-      </c>
+          <t>Diario Rio Negro</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lanzamiento Dot conecta</t>
+          <t>Plenario del CIN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Universidad Nacional de Río Negro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1681,12 +1657,16 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>INTERMEDIA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gobernador </t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>Sin especificar</t>
@@ -1694,15 +1674,19 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>General Roca</t>
+          <t>San Carlos de Bariloche</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Diario Rio Negro</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
+          <t>Sin especificar</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>El fin será contribuir con la elaboración de agendas institucionales y de política pública para el fortalecimiento de una educación superior democrática, federal y socialmente comprometida.</t>
+        </is>
+      </c>
       <c r="Q18" t="n">
         <v>50</v>
       </c>
@@ -1710,21 +1694,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plenario del CIN</t>
+          <t>Hackaton</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Universidad Nacional de Río Negro</t>
+          <t>SEEyA | Alkemy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1735,7 +1719,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Jóvenes y adultos</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1747,27 +1731,27 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gobernador </t>
+          <t>Gobernador | Secretaria de Energía</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>San Carlos de Bariloche</t>
+          <t>Cipolletti</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>Secretaría de Estado de Energía y Ambiente</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>El fin será contribuir con la elaboración de agendas institucionales y de política pública para el fortalecimiento de una educación superior democrática, federal y socialmente comprometida.</t>
+          <t>La actividad consistirá en una jornada colaborativa en la que los participantes, organizados en equipos, trabajarán sobre desafíos concretos para desarrollar una solución innovadora. A lo largo del encuentro, contarán con una instancia de ideación, desarrollo y preparación de la propuesta. Para finalizar, cada equipo presentará su solución ante un jurado, que seleccionará al equipo ganador.</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -1777,7 +1761,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1785,13 +1769,13 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hackaton</t>
+          <t>Jornada CFI - Gestión para el Desarrollo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SEEyA | Alkemy</t>
+          <t>CFI | SEEyA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1802,7 +1786,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Jóvenes y adultos</t>
+          <t>Jóvenes</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1812,39 +1796,35 @@
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Gobernador | Secretaria de Energía</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>Sin especificar</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Cipolletti</t>
+          <t>Alto Valle</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Secretaría de Estado de Energía y Ambiente</t>
+          <t>Sin especificar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>La actividad consistirá en una jornada colaborativa en la que los participantes, organizados en equipos, trabajarán sobre desafíos concretos para desarrollar una solución innovadora. A lo largo del encuentro, contarán con una instancia de ideación, desarrollo y preparación de la propuesta. Para finalizar, cada equipo presentará su solución ante un jurado, que seleccionará al equipo ganador.</t>
+          <t>Jornada de integración y paneles provinciales compuestas por visitas a sitios estratégicos para el desarrollo de la provincia, encuentros con funcionarias/os y referentes locales y actividades de integración grupal con los participantes de la formación Gestión para el Desarrollo.</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1858,7 +1838,7 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CFI | SEEyA</t>
+          <t>CFI | SEEyE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1907,21 +1887,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jornada CFI - Gestión para el Desarrollo</t>
+          <t>I Foro de la Juventud Rionegrina</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CFI | SEEyE</t>
+          <t>Varios</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1950,27 +1930,27 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Alto Valle</t>
+          <t>Cipolletti</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>Escuela Manuel Belgrano | CCC</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Jornada de integración y paneles provinciales compuestas por visitas a sitios estratégicos para el desarrollo de la provincia, encuentros con funcionarias/os y referentes locales y actividades de integración grupal con los participantes de la formación Gestión para el Desarrollo.</t>
+          <t xml:space="preserve">Primer Foro de la Juventud Rionegrina que reúne a jóvenes de toda la provincia para debatir, proponer y pensar la provincia. </t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1995,7 +1975,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Jóvenes</t>
+          <t>General</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2033,21 +2013,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>I Foro de la Juventud Rionegrina</t>
+          <t>Firma de Convienio con IAPG</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Varios</t>
+          <t>IAPG | SEEyA | Ministerio de Educación y DDHH</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2056,11 +2036,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>ALTA</t>
@@ -2071,46 +2047,42 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Cipolletti</t>
+          <t>General Roca</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Escuela Manuel Belgrano | CCC</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Primer Foro de la Juventud Rionegrina que reúne a jóvenes de toda la provincia para debatir, proponer y pensar la provincia. </t>
-        </is>
-      </c>
+          <t>CET 1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Firma de Convienio con IAPG</t>
+          <t>YPF por ONU HABITAT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAPG | SEEyA | Ministerio de Educación y DDHH</t>
+          <t>YPF | ONU-Hábitat | Secretaría de Ambiente | UNRN-Arquitectura</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2130,7 +2102,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>Sin especificar</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2140,7 +2112,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>CET 1</t>
+          <t>UNRN</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2151,23 +2123,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>YPF por ONU HABITAT</t>
+          <t>Maquetas V4LE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>YPF | ONU-Hábitat | Secretaría de Ambiente | UNRN-Arquitectura</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
@@ -2190,15 +2158,15 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>General Roca</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>UNRN</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
+          <t>Cipolletti</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Capacitación para el armado y el uso de las Maquetas V4LE.</t>
+        </is>
+      </c>
       <c r="Q26" t="n">
         <v>50</v>
       </c>
@@ -2206,7 +2174,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2241,67 +2209,16 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Cipolletti</t>
+          <t>General Roca</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Capacitación para el armado y el uso de las Maquetas V4LE.</t>
+          <t>Capacitación para docentes para el armado y uso de las Maquetas V4LE.</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>37</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Maquetas V4LE</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Sin especificar</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>General Roca</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Capacitación para docentes para el armado y uso de las Maquetas V4LE.</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
         <v>50</v>
       </c>
     </row>
